--- a/reports/excel/inverters/low_performing_inverters_report_22-05-2026.xlsx
+++ b/reports/excel/inverters/low_performing_inverters_report_22-05-2026.xlsx
@@ -18,10 +18,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-  </numFmts>
-  <fonts count="3">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,11 +31,8 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -47,11 +42,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001EA5FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E44545"/>
       </patternFill>
     </fill>
   </fills>
@@ -81,19 +71,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -463,20 +447,20 @@
   <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -551,66 +535,18 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="2" t="n">
-        <v>46164</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR ENGINEERING LOT 10</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>KLANG</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>3.8575</v>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>INVERTER(COM1-13)</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>ES2540045186</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>0.263</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0.2925</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>19.08</v>
-      </c>
-      <c r="M2" s="4" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>INVERTER(COM1-13) PSH IS 19.08% LOWER THAN THE HIGHEST INVERTER PSH IN MAJOR ENGINEERING LOT 10.</t>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>NO LOW-PERFORMING INVERTERS DETECTED</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N2"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:N2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>